--- a/data/trans_orig/IP2003-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP2003-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16524</t>
+          <t>16405</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30947</t>
+          <t>30620</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14931</t>
+          <t>14845</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28449</t>
+          <t>28909</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>34208</t>
+          <t>35844</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>54844</t>
+          <t>54991</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,18%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>98059</t>
+          <t>98386</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>112482</t>
+          <t>112601</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,01%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>115058</t>
+          <t>114598</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>128576</t>
+          <t>128662</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>79,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>217669</t>
+          <t>217522</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>238305</t>
+          <t>236669</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>86,85%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31612</t>
+          <t>31680</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49424</t>
+          <t>49589</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24609</t>
+          <t>24173</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40771</t>
+          <t>40157</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>60224</t>
+          <t>59647</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>83948</t>
+          <t>84289</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,57%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>136360</t>
+          <t>136195</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>154172</t>
+          <t>154104</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,4%</t>
+          <t>73,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,98%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>164131</t>
+          <t>164745</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>180293</t>
+          <t>180729</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,1%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>88,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>306738</t>
+          <t>306397</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>330462</t>
+          <t>331039</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>78,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,73%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20638</t>
+          <t>20364</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35174</t>
+          <t>35373</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14705</t>
+          <t>15278</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28259</t>
+          <t>27589</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>39051</t>
+          <t>38746</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>59442</t>
+          <t>59451</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>95558</t>
+          <t>95359</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>110094</t>
+          <t>110368</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>72,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>84,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>111083</t>
+          <t>111753</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>124637</t>
+          <t>124064</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>80,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>210632</t>
+          <t>210623</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>231023</t>
+          <t>231328</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>85,65%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15564</t>
+          <t>15851</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31779</t>
+          <t>30957</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16740</t>
+          <t>16454</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32342</t>
+          <t>32431</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>36421</t>
+          <t>35959</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>58972</t>
+          <t>58277</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,69%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>167739</t>
+          <t>168561</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>183954</t>
+          <t>183667</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>164797</t>
+          <t>164708</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>180399</t>
+          <t>180685</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>83,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>337685</t>
+          <t>338380</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>360236</t>
+          <t>360698</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>85,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>90,93%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>98898</t>
+          <t>98461</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>129850</t>
+          <t>130729</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>84568</t>
+          <t>83875</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>112638</t>
+          <t>112949</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>190643</t>
+          <t>190555</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>232740</t>
+          <t>231108</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,38%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>515190</t>
+          <t>514311</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>546142</t>
+          <t>546579</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>79,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>572252</t>
+          <t>571941</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>600322</t>
+          <t>601015</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1097190</t>
+          <t>1098822</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1139287</t>
+          <t>1139375</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,5%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14818</t>
+          <t>15257</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29132</t>
+          <t>29676</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18170</t>
+          <t>17693</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>33411</t>
+          <t>33936</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>36097</t>
+          <t>36073</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>56976</t>
+          <t>56161</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,4%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>104036</t>
+          <t>103492</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>118350</t>
+          <t>117911</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>77,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>108716</t>
+          <t>108191</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>123957</t>
+          <t>124434</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>76,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>87,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>218319</t>
+          <t>219134</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>239198</t>
+          <t>239222</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>79,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>86,9%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30083</t>
+          <t>30421</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47816</t>
+          <t>47779</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22414</t>
+          <t>22332</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39455</t>
+          <t>39644</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>57192</t>
+          <t>58277</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>81065</t>
+          <t>80550</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>19,92%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>143703</t>
+          <t>143740</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>161436</t>
+          <t>161098</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>75,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>173298</t>
+          <t>173109</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>190339</t>
+          <t>190421</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>81,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>323207</t>
+          <t>323722</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>347080</t>
+          <t>345995</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>80,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>85,58%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14571</t>
+          <t>14937</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28482</t>
+          <t>28795</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14782</t>
+          <t>14332</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28420</t>
+          <t>27588</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32858</t>
+          <t>32529</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>51596</t>
+          <t>50846</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,12%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>116176</t>
+          <t>115863</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>130087</t>
+          <t>129721</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>80,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>123873</t>
+          <t>124705</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>137511</t>
+          <t>137961</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,34%</t>
+          <t>81,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>245355</t>
+          <t>246105</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>264093</t>
+          <t>264422</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>89,05%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22786</t>
+          <t>22119</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40920</t>
+          <t>39607</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11493</t>
+          <t>11239</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24935</t>
+          <t>24999</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>39149</t>
+          <t>38028</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>61221</t>
+          <t>59793</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,34%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>152627</t>
+          <t>153940</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>170761</t>
+          <t>171428</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>79,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>88,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>171331</t>
+          <t>171267</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>184773</t>
+          <t>185027</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>328592</t>
+          <t>330020</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>350664</t>
+          <t>351785</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>84,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>90,24%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>96409</t>
+          <t>96632</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>127193</t>
+          <t>128679</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>79135</t>
+          <t>79780</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>109947</t>
+          <t>109427</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>182712</t>
+          <t>182534</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>225701</t>
+          <t>225112</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,48%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>535698</t>
+          <t>534212</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>566482</t>
+          <t>566259</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,81%</t>
+          <t>80,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>593493</t>
+          <t>594013</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>624305</t>
+          <t>623660</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>84,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1140630</t>
+          <t>1141219</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1183619</t>
+          <t>1183797</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,64%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9436</t>
+          <t>8825</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21600</t>
+          <t>22106</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8043</t>
+          <t>8235</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20678</t>
+          <t>20524</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19845</t>
+          <t>20453</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>37251</t>
+          <t>37567</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,24%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>103069</t>
+          <t>102563</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>115233</t>
+          <t>115844</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>118432</t>
+          <t>118586</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>131067</t>
+          <t>130875</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>226528</t>
+          <t>226212</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>243934</t>
+          <t>243326</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,25%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19711</t>
+          <t>20326</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35812</t>
+          <t>36287</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23218</t>
+          <t>22945</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39532</t>
+          <t>40271</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>46830</t>
+          <t>47530</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>71148</t>
+          <t>69935</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,31%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>157424</t>
+          <t>156949</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>173525</t>
+          <t>172910</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,47%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>171145</t>
+          <t>170406</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>187459</t>
+          <t>187732</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>80,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>332765</t>
+          <t>333978</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>357083</t>
+          <t>356383</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>82,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,23%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11865</t>
+          <t>11781</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23605</t>
+          <t>24220</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15211</t>
+          <t>14412</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28765</t>
+          <t>28819</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29969</t>
+          <t>29276</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>48904</t>
+          <t>48248</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,63%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>124562</t>
+          <t>123947</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>136302</t>
+          <t>136386</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>131662</t>
+          <t>131608</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>145216</t>
+          <t>146015</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,07%</t>
+          <t>82,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>259690</t>
+          <t>260346</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>278625</t>
+          <t>279318</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,51%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22121</t>
+          <t>23337</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40726</t>
+          <t>41244</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18260</t>
+          <t>18118</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34591</t>
+          <t>33690</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>44606</t>
+          <t>45231</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>69523</t>
+          <t>68959</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,0%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>151757</t>
+          <t>151239</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>170362</t>
+          <t>169146</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,84%</t>
+          <t>78,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>156090</t>
+          <t>156991</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>172421</t>
+          <t>172563</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>82,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>313640</t>
+          <t>314204</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>338557</t>
+          <t>337932</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,2%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>74365</t>
+          <t>73987</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>103934</t>
+          <t>105283</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>78067</t>
+          <t>77560</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>107974</t>
+          <t>108202</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>160639</t>
+          <t>158663</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>202155</t>
+          <t>200926</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,78%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>554621</t>
+          <t>553272</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>584190</t>
+          <t>584568</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>88,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>592921</t>
+          <t>592693</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>622828</t>
+          <t>623335</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1157294</t>
+          <t>1158523</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1198810</t>
+          <t>1200786</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>88,33%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7280</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17925</t>
+          <t>18060</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4045</t>
+          <t>3978</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47774</t>
+          <t>49435</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>36,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15221</t>
+          <t>14648</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>59264</t>
+          <t>60932</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>24,2%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>97145</t>
+          <t>97010</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>107790</t>
+          <t>107989</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>88983</t>
+          <t>87322</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>132712</t>
+          <t>132779</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,07%</t>
+          <t>63,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>192563</t>
+          <t>190895</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>236606</t>
+          <t>237179</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>75,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>94,18%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12038</t>
+          <t>11667</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25884</t>
+          <t>25403</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26832</t>
+          <t>26129</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>53177</t>
+          <t>55171</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>41973</t>
+          <t>42569</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>72892</t>
+          <t>72914</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>161014</t>
+          <t>161495</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>174860</t>
+          <t>175231</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>195965</t>
+          <t>193971</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>222310</t>
+          <t>223013</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>77,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>363148</t>
+          <t>363126</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>394067</t>
+          <t>393471</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7120,7 +7120,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,24%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>37627</t>
+          <t>37811</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>109286</t>
+          <t>107582</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>58,14%</t>
+          <t>57,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23778</t>
+          <t>24291</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44284</t>
+          <t>44859</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>68894</t>
+          <t>68217</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>161219</t>
+          <t>158177</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>42,56%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>78701</t>
+          <t>80405</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>150360</t>
+          <t>150176</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>41,86%</t>
+          <t>42,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>139419</t>
+          <t>138844</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>159925</t>
+          <t>159412</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>75,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>86,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>210471</t>
+          <t>213513</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>302796</t>
+          <t>303473</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>56,63%</t>
+          <t>57,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>81,65%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14135</t>
+          <t>13519</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29091</t>
+          <t>28065</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13730</t>
+          <t>13539</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27978</t>
+          <t>28516</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>30793</t>
+          <t>30031</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>52133</t>
+          <t>51762</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,05%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>137025</t>
+          <t>138051</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>151981</t>
+          <t>152597</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,49%</t>
+          <t>83,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>149885</t>
+          <t>149347</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>164133</t>
+          <t>164324</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>291846</t>
+          <t>292217</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>313186</t>
+          <t>313948</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>91,27%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>83378</t>
+          <t>85095</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>192532</t>
+          <t>196712</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>85121</t>
+          <t>84499</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>138824</t>
+          <t>142608</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>181128</t>
+          <t>180719</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>298933</t>
+          <t>303305</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,61%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>463539</t>
+          <t>459359</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>572693</t>
+          <t>570976</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,65%</t>
+          <t>70,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>608641</t>
+          <t>604857</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>662344</t>
+          <t>662966</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,43%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1104603</t>
+          <t>1100231</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1222408</t>
+          <t>1222817</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,7%</t>
+          <t>78,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>87,12%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP2003-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP2003-Habitat-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>20989</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>14758</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>29184</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>14,63%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>10,28%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>20,34%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>23058</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>16405</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>30620</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>17142</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>31377</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>17,87%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>12,72%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>23,74%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>20989</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>14845</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>28909</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>14,63%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>35844</t>
+          <t>34832</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>54991</t>
+          <t>53661</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>19,69%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>122518</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>114323</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>128749</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>85,37%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>79,66%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>89,72%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>155</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>105948</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>98386</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>112601</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>97629</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>111864</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>82,13%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>76,26%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>87,28%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>122518</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>114598</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>128662</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>85,37%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>75,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>217522</t>
+          <t>218852</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>236669</t>
+          <t>237681</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>80,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>87,22%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>143507</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>143507</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>143507</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>129006</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>129006</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>129006</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>213</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>143507</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>143507</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>143507</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>31474</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>24177</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>40236</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>15,36%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>11,8%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>19,64%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>40000</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>31680</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>49589</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>32419</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>49982</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>21,53%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>17,05%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>26,69%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>31474</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>24173</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>40157</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>15,36%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>59647</t>
+          <t>60600</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>84289</t>
+          <t>83475</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,37%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>173428</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>164666</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>180725</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>84,64%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>80,36%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>88,2%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>145784</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>136195</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>154104</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>135802</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>153365</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>78,47%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>73,31%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>82,95%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>264</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>173428</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>164745</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>180729</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>84,64%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>73,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>306397</t>
+          <t>307211</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>331039</t>
+          <t>330086</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>78,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>84,49%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>311</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>204902</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>204902</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>204902</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>297</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>185784</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>185784</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>185784</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>311</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>204902</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>204902</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>204902</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>21053</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>15188</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>28290</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>15,11%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>10,9%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>20,3%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>27425</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>20364</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>35373</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>21110</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>35139</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>20,98%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>15,58%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>27,06%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>21053</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>15278</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>27589</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>15,11%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>38746</t>
+          <t>38734</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>59451</t>
+          <t>57994</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>21,47%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>118289</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>111052</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>124154</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>84,89%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>79,7%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>89,1%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>173</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>103307</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>95359</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>110368</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>95593</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>109622</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>79,02%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>72,94%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>84,42%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>118289</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>111753</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>124064</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>84,89%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>73,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>210623</t>
+          <t>212080</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>231328</t>
+          <t>231340</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,99%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>85,66%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>139342</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>139342</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>139342</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>217</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>130732</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>130732</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>130732</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>139342</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>139342</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>139342</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>24019</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>17295</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>32484</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>12,18%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>8,77%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>16,48%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>22822</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>15851</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>30957</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>15919</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>31644</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>11,44%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>7,94%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>15,52%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>24019</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>16454</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>32431</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>12,18%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>35959</t>
+          <t>37345</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>58277</t>
+          <t>59068</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,89%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>173120</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>164655</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>179844</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>87,82%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>83,52%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>91,23%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>232</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>176696</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>168561</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>183667</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>167874</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>183599</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>88,56%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>84,48%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>92,06%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>256</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>173120</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>164708</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>180685</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>87,82%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>84,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>338380</t>
+          <t>337589</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>360698</t>
+          <t>359312</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>90,59%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>197139</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>197139</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>197139</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>261</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>199518</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>199518</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>199518</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>197139</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>197139</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>197139</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>97535</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>83687</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>111819</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>14,24%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>12,22%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>16,33%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>169</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>113305</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>98461</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>130729</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>97996</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>128552</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>17,57%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>15,26%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>20,27%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>97535</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>83875</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>112949</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>14,24%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>190555</t>
+          <t>189962</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>231108</t>
+          <t>232012</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,45%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>885</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>587355</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>573071</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>601203</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>85,76%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>83,67%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>87,78%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>794</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>531735</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>514311</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>546579</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>516488</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>547044</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>82,43%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>79,73%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>84,74%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>885</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>587355</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>571941</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>601015</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>85,76%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>80,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1098822</t>
+          <t>1097918</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1139375</t>
+          <t>1139968</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>85,72%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1030</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>684890</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>684890</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>684890</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>963</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>645040</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>645040</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>645040</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1030</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>684890</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>684890</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>684890</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>24946</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>17819</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>33684</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>17,55%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>12,54%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>23,7%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>21365</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>15257</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>29676</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>14435</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>29206</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>16,04%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>11,46%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>22,28%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>24946</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>17693</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>33936</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>17,55%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>36073</t>
+          <t>37171</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>56161</t>
+          <t>58448</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>21,23%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>117181</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>108443</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>124308</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>82,45%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>76,3%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>87,46%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>111803</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>103492</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>117911</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>103962</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>118733</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>83,96%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>77,72%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>88,54%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>117181</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>108191</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>124434</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>82,45%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>78,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>219134</t>
+          <t>216847</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>239222</t>
+          <t>238124</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>78,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>86,5%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>142127</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>142127</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>142127</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>181</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>133168</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>133168</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>133168</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>142127</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>142127</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>142127</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>29790</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>22620</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>38997</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>14,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>10,63%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>18,33%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>38399</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>30421</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>47779</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>29868</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>48136</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>20,05%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>15,88%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>24,95%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>29790</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>22332</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>39644</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>14,0%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>58277</t>
+          <t>55868</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>80550</t>
+          <t>80105</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,81%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>182963</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>173756</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>190133</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>86,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>81,67%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>89,37%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>238</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>153120</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>143740</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>161098</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>143383</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>161651</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>79,95%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>75,05%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>84,12%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>182963</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>173109</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>190421</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>86,0%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>74,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>323722</t>
+          <t>324167</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>345995</t>
+          <t>348404</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,08%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>86,18%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>212753</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>212753</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>212753</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>296</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>191519</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>191519</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>191519</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>308</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>212753</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>212753</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>212753</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3361,67 +3361,67 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>20624</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>14287</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>28469</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>13,54%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>9,38%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>18,69%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>20635</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>14937</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>28795</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>14828</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>27780</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>14,26%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>10,33%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>19,91%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>20624</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>14332</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>27588</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>13,54%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32529</t>
+          <t>32213</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>50846</t>
+          <t>50947</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,16%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>131669</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>123824</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>138006</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>86,46%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>81,31%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>90,62%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>193</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>124023</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>115863</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>129721</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>116878</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>129830</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>85,74%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>80,09%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>89,67%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>204</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>131669</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>124705</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>137961</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>86,46%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>80,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>246105</t>
+          <t>246004</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>264422</t>
+          <t>264738</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>82,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>89,15%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>152293</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>152293</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>152293</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>225</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>144658</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>144658</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>144658</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>152293</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>152293</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>152293</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>17437</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>11552</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>25264</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>8,88%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>5,89%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>12,87%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>30832</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>22119</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>39607</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>23156</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>40475</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>15,93%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>11,43%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>20,46%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>17437</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>11239</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>24999</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>8,88%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>38028</t>
+          <t>37405</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>59793</t>
+          <t>60289</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,47%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>178829</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>171002</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>184714</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>91,12%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>87,13%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>94,11%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>213</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>162715</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>153940</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>171428</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>153072</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>170391</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>84,07%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>79,54%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>88,57%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>178829</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>171267</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>185027</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>91,12%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>79,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>330020</t>
+          <t>329524</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>351785</t>
+          <t>352408</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,66%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,4%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>196266</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>196266</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>196266</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>252</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>193547</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>193547</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>193547</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>266</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>196266</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>196266</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>196266</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>92797</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>79432</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>108594</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>13,19%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>11,29%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>15,44%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>158</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>111231</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>96632</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>128679</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>95300</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>127320</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>16,78%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>14,58%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>19,41%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>92797</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>79780</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>109427</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>13,19%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>182534</t>
+          <t>181667</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>225112</t>
+          <t>225261</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,49%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>868</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>610643</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>594846</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>624008</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>86,81%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>84,56%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>88,71%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>796</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>551660</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>534212</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>566259</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>535571</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>567591</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>83,22%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>80,59%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>85,42%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>868</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>610643</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>594013</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>623660</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>86,81%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>80,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1141219</t>
+          <t>1141070</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1183797</t>
+          <t>1184664</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>86,7%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>703440</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>703440</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>703440</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>954</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>662891</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>662891</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>662891</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1004</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>703440</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>703440</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>703440</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>13252</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8149</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>19526</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>9,53%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>5,86%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>14,04%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>14530</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>8825</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>22106</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>9325</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>22007</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>11,66%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>7,08%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>17,73%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>13252</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>8235</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>20524</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>9,53%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20453</t>
+          <t>20195</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>37567</t>
+          <t>36496</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>13,84%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>125858</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>119584</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>130961</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>90,47%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>85,96%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>94,14%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>154</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>110139</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>102563</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>115844</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>102662</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>115344</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>88,34%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>82,27%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>92,92%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>125858</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>118586</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>130875</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>90,47%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>82,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>226212</t>
+          <t>227283</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>243326</t>
+          <t>243584</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,34%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>139110</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>139110</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>139110</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>173</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>124669</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>124669</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>124669</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>139110</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>139110</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>139110</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>30912</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>23517</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>39706</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>14,67%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>11,16%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>18,85%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>26707</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>20326</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>36287</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>19387</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>35130</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>13,82%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>10,52%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>18,78%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>30912</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>22945</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>40271</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>14,67%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>47530</t>
+          <t>47408</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>69935</t>
+          <t>71067</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,59%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>179765</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>170971</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>187160</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>85,33%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>81,15%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>88,84%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>269</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>166529</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>156949</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>172910</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>158106</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>173849</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>86,18%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>81,22%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>89,48%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>267</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>179765</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>170406</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>187732</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>85,33%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,88%</t>
+          <t>81,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>333978</t>
+          <t>332846</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>356383</t>
+          <t>356505</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>88,26%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>311</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>210677</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>210677</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>210677</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>310</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>193236</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>193236</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>193236</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>311</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>210677</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>210677</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>210677</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>21243</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>14983</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>29503</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>13,24%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>9,34%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>18,39%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>16937</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>11781</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>24220</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>11784</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>23969</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>11,43%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>7,95%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>16,35%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>21243</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>14412</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>28819</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>13,24%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>8,98%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29276</t>
+          <t>30118</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>48248</t>
+          <t>49000</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,88%</t>
         </is>
       </c>
     </row>
@@ -5416,74 +5416,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>139184</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>130924</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>145444</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>86,76%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>81,61%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>90,66%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>217</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>131230</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>123947</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>136386</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>124198</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>136383</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>88,57%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>83,65%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>83,82%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>92,05%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>139184</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>131608</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>146015</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>86,76%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>82,04%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>91,02%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>425</t>
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>260346</t>
+          <t>259594</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>279318</t>
+          <t>278476</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,24%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>160427</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>160427</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>160427</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>244</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>148167</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>148167</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>148167</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>160427</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>160427</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>160427</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>25494</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>18378</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>33981</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>13,37%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>9,64%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>17,82%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>30781</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>23337</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>41244</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>22898</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>40883</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>15,99%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>12,12%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>21,43%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>25494</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>18118</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>33690</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>13,37%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>45231</t>
+          <t>44457</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>68959</t>
+          <t>68556</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,89%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>165187</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>156700</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>172303</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>86,63%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>82,18%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>90,36%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>220</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>161702</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>151239</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>169146</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>151600</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>169585</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>84,01%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>78,57%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>87,88%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>165187</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>156991</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>172563</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>86,63%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>88,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>314204</t>
+          <t>314607</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>337932</t>
+          <t>338706</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>88,4%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>190681</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>190681</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>190681</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>261</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>192483</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>192483</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>192483</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>190681</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>190681</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>190681</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>90901</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>77447</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>106142</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>12,97%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>11,05%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>15,14%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>88955</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>73987</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>105283</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>73998</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>103586</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>13,51%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>11,23%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>15,99%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>90901</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>77560</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>108202</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>12,97%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>158663</t>
+          <t>159691</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>200926</t>
+          <t>201619</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,83%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>874</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>609994</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>594753</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>623448</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>87,03%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>84,86%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>88,95%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>860</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>569600</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>553272</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>584568</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>554969</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>584557</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>86,49%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>84,01%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>88,77%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>874</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>609994</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>592693</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>623335</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>87,03%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1158523</t>
+          <t>1157830</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1200786</t>
+          <t>1199758</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,25%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>700895</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>700895</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>700895</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>988</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>658555</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>658555</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>658555</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>700895</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>700895</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>700895</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>12725</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2813</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>37163</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>10,36%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2,29%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>30,24%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>11817</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>7081</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>18060</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>10,27%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>6,15%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>15,69%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>15885</t>
+          <t>12133</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3978</t>
+          <t>7637</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>49435</t>
+          <t>18750</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>27702</t>
+          <t>24858</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14648</t>
+          <t>15032</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>60932</t>
+          <t>48323</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>19,95%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>110154</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>85716</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>120066</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>89,64%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>69,76%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>97,71%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>171</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>103253</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>97010</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>107989</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>89,73%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>84,31%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>93,85%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>120872</t>
+          <t>107169</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>87322</t>
+          <t>100552</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>132779</t>
+          <t>111665</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>63,85%</t>
+          <t>84,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>224125</t>
+          <t>217323</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>190895</t>
+          <t>193858</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>237179</t>
+          <t>227149</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>80,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>93,79%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>122879</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>122879</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>122879</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>115070</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>115070</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>115070</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>136757</t>
+          <t>119302</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>136757</t>
+          <t>119302</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>136757</t>
+          <t>119302</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>251827</t>
+          <t>242181</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>251827</t>
+          <t>242181</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>251827</t>
+          <t>242181</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>33817</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>24095</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>50730</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>14,54%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>10,36%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>21,81%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>17615</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>11667</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>25403</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>9,43%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>6,24%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>13,59%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>37164</t>
+          <t>17892</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26129</t>
+          <t>11411</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>55171</t>
+          <t>26669</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>54779</t>
+          <t>51709</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>42569</t>
+          <t>38872</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>72914</t>
+          <t>69353</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,74%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>198739</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>181826</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>208461</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>85,46%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>78,19%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>89,64%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>248</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>169283</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>161495</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>175231</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>90,57%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>86,41%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>93,76%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>211978</t>
+          <t>163776</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>193971</t>
+          <t>154999</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>223013</t>
+          <t>170257</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,86%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>381261</t>
+          <t>362515</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>363126</t>
+          <t>344871</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>393471</t>
+          <t>375352</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>87,52%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>83,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,62%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>232556</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>232556</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>232556</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>186898</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>186898</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>186898</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>249142</t>
+          <t>181668</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>249142</t>
+          <t>181668</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>249142</t>
+          <t>181668</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>436040</t>
+          <t>414224</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>436040</t>
+          <t>414224</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>436040</t>
+          <t>414224</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>29975</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>21701</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>41519</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>17,93%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>12,98%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>24,84%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>63290</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>37811</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>107582</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>33,67%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>20,11%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>57,23%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>32596</t>
+          <t>36965</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24291</t>
+          <t>27789</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44859</t>
+          <t>46904</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>95885</t>
+          <t>66941</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>68217</t>
+          <t>54169</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>158177</t>
+          <t>82079</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>25,5%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>137172</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>125628</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>145446</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>82,07%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>75,16%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>87,02%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>173</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>124697</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>80405</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>150176</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>66,33%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>42,77%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>79,89%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>151107</t>
+          <t>117708</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>138844</t>
+          <t>107769</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>159412</t>
+          <t>126884</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>76,1%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>82,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>275805</t>
+          <t>254879</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>213513</t>
+          <t>239741</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>303473</t>
+          <t>267651</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>74,2%</t>
+          <t>79,2%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>57,44%</t>
+          <t>74,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>83,17%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>167147</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>167147</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>167147</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>187987</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>187987</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>187987</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>183703</t>
+          <t>154673</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>183703</t>
+          <t>154673</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>183703</t>
+          <t>154673</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>371690</t>
+          <t>321820</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>371690</t>
+          <t>321820</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>371690</t>
+          <t>321820</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>18393</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>12925</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>25853</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>11,04%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>7,76%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>15,52%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>20326</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>13519</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>28065</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>12,24%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>8,14%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>16,89%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19720</t>
+          <t>20590</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13539</t>
+          <t>14219</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28516</t>
+          <t>28881</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>40046</t>
+          <t>38983</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>30031</t>
+          <t>28861</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>51762</t>
+          <t>49270</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>14,85%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>148215</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>140755</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>153683</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>88,96%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>84,48%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>92,24%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>209</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>145790</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>138051</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>152597</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>87,76%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>83,11%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>91,86%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>158143</t>
+          <t>144581</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>149347</t>
+          <t>136290</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>164324</t>
+          <t>150952</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>82,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>303933</t>
+          <t>292796</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>292217</t>
+          <t>282509</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>313948</t>
+          <t>302918</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>91,3%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>166608</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>166608</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>166608</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>236</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>166116</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>166116</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>166116</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>177863</t>
+          <t>165171</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>177863</t>
+          <t>165171</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>177863</t>
+          <t>165171</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>343979</t>
+          <t>331779</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>343979</t>
+          <t>331779</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>343979</t>
+          <t>331779</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>94910</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>77347</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>124939</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>13,77%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>11,22%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>18,13%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>120</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>113048</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>85095</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>196712</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>17,23%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>12,97%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>29,98%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>105364</t>
+          <t>87580</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>84499</t>
+          <t>73954</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>142608</t>
+          <t>103379</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>218412</t>
+          <t>182490</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>180719</t>
+          <t>159899</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>303305</t>
+          <t>213725</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>16,31%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>837</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>594280</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>564251</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>611843</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>86,23%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>81,87%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>88,78%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>801</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>543023</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>459359</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>570976</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>82,77%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>70,02%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>87,03%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>837</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>642101</t>
+          <t>533234</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>604857</t>
+          <t>517435</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>662966</t>
+          <t>546860</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>83,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1185124</t>
+          <t>1127514</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1100231</t>
+          <t>1096279</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1222817</t>
+          <t>1150105</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>83,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>87,79%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>946</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>689190</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>689190</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>689190</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>921</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>656071</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>656071</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>656071</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>946</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>747465</t>
+          <t>620814</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>747465</t>
+          <t>620814</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>747465</t>
+          <t>620814</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1403536</t>
+          <t>1310004</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1403536</t>
+          <t>1310004</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1403536</t>
+          <t>1310004</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
